--- a/docs/gantt.xlsx
+++ b/docs/gantt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ралина\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7778C5FD-980A-4EF9-96ED-AF7213ABAEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED9F778-24BE-44B6-BC71-26EB5D5D7BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12740" yWindow="880" windowWidth="11540" windowHeight="12700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="1180" windowWidth="11540" windowHeight="13600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Гантт" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>План проекта (Гантт) · пары 5–30 · магазин обуви</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>0907-43</t>
+  </si>
+  <si>
+    <t>сделано</t>
   </si>
 </sst>
 </file>
@@ -265,12 +268,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -583,22 +586,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -631,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -648,7 +651,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -842,10 +845,10 @@
       <c r="A19" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E19" t="s">

--- a/docs/gantt.xlsx
+++ b/docs/gantt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ралина\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED9F778-24BE-44B6-BC71-26EB5D5D7BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC4BBFA-D286-49A0-A2FF-94DA7BDB9316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="1180" windowWidth="11540" windowHeight="13600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="280" windowWidth="11540" windowHeight="13600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Гантт" sheetId="1" r:id="rId1"/>
@@ -651,7 +651,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -668,7 +668,7 @@
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
